--- a/output/pdf_financials_xlsx/JAB.P.xlsx
+++ b/output/pdf_financials_xlsx/JAB.P.xlsx
@@ -735,10 +735,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.0009700000000000001</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00104</v>
       </c>
     </row>
     <row r="13">
@@ -1178,10 +1178,10 @@
         <v>-0.049788</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.044699</v>
+        <v>-0.043729</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.041621</v>
+        <v>-0.040581</v>
       </c>
     </row>
     <row r="28">
@@ -1234,10 +1234,10 @@
         <v>-0.049788</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.044699</v>
+        <v>-0.043729</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.041621</v>
+        <v>-0.040581</v>
       </c>
     </row>
     <row r="30">
@@ -1362,19 +1362,19 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.216474</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.176668</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.129897</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.083797</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.042527</v>
       </c>
     </row>
     <row r="35">
@@ -1416,19 +1416,19 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.216474</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.176668</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.129897</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.083797</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.042527</v>
       </c>
     </row>
     <row r="37">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
